--- a/Insurance Rate Data Scraper/output/oh_all_companies_search.xlsx
+++ b/Insurance Rate Data Scraper/output/oh_all_companies_search.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG992"/>
+  <dimension ref="A1:AG1034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63713,6 +63713,2691 @@
         </is>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>SFMA-134927661</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>134927661</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>25143</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>HO-50149</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P993" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE993" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG993" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134927661</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>GECC-134949965</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>134949965</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>189 - Auto Forms</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P994" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE994" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG994" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134949965</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>GECC-134964301</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>134964301</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>203 - Comm Rate/Rule</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P995" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE995" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG995" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134964301</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>GECC-134965692</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>134965692</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>205 - Auto Rate</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P996" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE996" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG996" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134965692</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>GECC-134980422</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>134980422</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>206A - Auto Forms</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P997" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE997" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG997" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134980422</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>GECC-134911467</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>134911467</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>554A - Commercial Form</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P998" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE998" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG998" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134911467</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>PRGS-134956984</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>134956984</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>OH TT 202102</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P999" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE999" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG999" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134956984</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>PRGS-134934052</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>134934052</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>16322</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>PUP OH 202601 PDIC</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>09.0004 Pet Insurance Plans</t>
+        </is>
+      </c>
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1000" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1000" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1000" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134934052</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>PRGS-134939057</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>134939057</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>37834</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>Commercial Auto Program</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Closed - FILE &amp; USE</t>
+        </is>
+      </c>
+      <c r="P1001" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1001" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1001" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134939057</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>PRGS-134931750</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>134931750</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>37834</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>Businessowners</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1002" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1002" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1002" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134931750</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>PRGS-134929285</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>134929285</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>37834</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>Commercial Auto</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1003" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1003" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1003" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134929285</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>PRGS-134943272</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>134943272</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>Progressive Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Progressive</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>37834</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>Commercial Auto Program</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1004" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1004" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1004" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134943272</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>ALSE-134916776</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>134916776</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>29688</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>AFCIC PPA</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1005" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1005" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1005" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134916776</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>ALSE-134990846</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>134990846</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>Allstate Northbrook Indemnity Company</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>Allstate</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>36455</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>ANIC PPA</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1006" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1006" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1006" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134990846</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>TRVD-G134987915</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>134992213</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>Travelers Casualty and Surety Company of America</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>31194</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>EPL Form Filing 2026-03-0721</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>17.0010 Employment Practices Liability</t>
+        </is>
+      </c>
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1007" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1007" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1007" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134992213</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>TRVD-134891939</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>134891939</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>CLM Div. 3 Crime &amp; Fidelity</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>26.0001 Commercial Burglary and Theft</t>
+        </is>
+      </c>
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>Non-Adopt or Delay Adopt Bureau Filings (no other changes)</t>
+        </is>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1008" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1008" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1008" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134891939</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>TRVD-134922684</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>134922684</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>CLM Div. 6 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>Non-Adopt or Delay Adopt Bureau Filings (no other changes)</t>
+        </is>
+      </c>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1009" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1009" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1009" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134922684</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>TRVD-134989084</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>134989084</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>17.1001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1010" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1010" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1010" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134989084</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>TRVD-135002576</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>135002576</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>Travelers Property Casualty Company of America</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>25674</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>Excess Follow-Form and Umbrella Liability</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1011" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1011" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1011" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135002576</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>LBPM-135031897</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>135031897</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>23043</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>Homeowners</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1012" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1012" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1012" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135031897</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>LINU-135005888</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>135005888</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>23043</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>ProShield Phase VI</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>17.2006 Directors &amp; Officers Liability</t>
+        </is>
+      </c>
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1013" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1013" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1013" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135005888</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>LWCM-134898252</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>134898252</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1014" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1014" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1014" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134898252</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>LBPM-134925838</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>134925838</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Liberty Mutual</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>Personal Auto</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1015" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1015" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1015" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134925838</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>LBPM-134962613</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>134962613</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Safeco</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>39012</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>Motorcycle</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1016" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1016" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1016" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134962613</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>LBRC-134906086</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>134906086</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>General Insurance</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>24732</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>Businessowners</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1017" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1017" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1017" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134906086</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>LBRC-134929132</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>134929132</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>First National Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>First National Insurance</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>17.0001 Commercial General Liability</t>
+        </is>
+      </c>
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1018" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1018" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1018" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134929132</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>LBRC-134950960</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>134950960</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>First National Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>First National Insurance</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>24724</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>Commercial Property</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>01.0001 Commercial Property (Fire and Allied Lines)</t>
+        </is>
+      </c>
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1019" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1019" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1019" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134950960</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>LWCM-135002379</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>135002379</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>42404</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1020" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1020" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1020" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135002379</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>LINU-134904945</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>134904945</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Underwriters Inc.</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Liberty Insurance</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>19917</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>Excess DIC Side-A Only Executive Advantage Policy</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>17.2020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1021" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1021" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1021" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134904945</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>USAA-134941386</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>134941459</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Garrison</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>21253</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>UMBRELLA</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>17.1021 Personal Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1022" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1022" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1022" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134941459</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>FARM-134954764</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>134954764</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>Commercial Auto Flex - Farmers</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>20.0001 Business Auto</t>
+        </is>
+      </c>
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1023" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1023" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1023" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134954764</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>FARM-134978060</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>134978060</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>Commercial Businessowners - Hab and ROS</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>05.0002 Businessowners</t>
+        </is>
+      </c>
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1024" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1024" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1024" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134978060</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>FARM-134955336</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>134955336</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>21652</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>UMB</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>17.0021 Personal Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1025" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1025" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1025" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134955336</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>FMHL-134969428</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>134969428</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Farmers Mutual Hail Insurance Company, SI</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>13897</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>Private Product Name Change Form Filing</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>02.1001 Crop-Hail Non-Federally Reinsured Only</t>
+        </is>
+      </c>
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1026" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1026" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1026" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134969428</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>FAIG-134929973</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>134929973</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Farmers Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>26298</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>Private Passenger Auto</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1027" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1027" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1027" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134929973</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>FARM-134941207</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>134941207</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Farmers</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>NGHO / LHO</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1028" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1028" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1028" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134941207</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>FARM-134877598</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>134877598</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Fire Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>21660</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>BOP360</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>05.0003 Commercial Package</t>
+        </is>
+      </c>
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1029" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1029" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1029" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134877598</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>FARM-134893930</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>134893930</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>21709</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>Form/Rate/Rule</t>
+        </is>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1030" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1030" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1030" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134893930</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>FARM-135031846</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>135031846</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Truck Insurance Exchange</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>21709</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>Commercial Umbrella</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>17.0020 Commercial Umbrella and Excess</t>
+        </is>
+      </c>
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>Pending Response</t>
+        </is>
+      </c>
+      <c r="P1031" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1031" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1031" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135031846</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>NWPP-G135005082</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>135005905</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Nationwide Agribusiness Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Nationwide</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>28223</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>Auto Comm AG Operations</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>20.0000 Commercial Auto Combinations</t>
+        </is>
+      </c>
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>Non-Adopt or Delay Adopt Bureau Filings (no other changes)</t>
+        </is>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1032" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1032" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1032" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135005905</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>AMLX-134957889</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>134957889</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>American Family Home Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>American Family</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>23450</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>Community Association Underwriters</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>05.0000 CMP Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>Form/Rule</t>
+        </is>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1033" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE1033" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1033" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=134957889</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>TRVD-G134997247</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>135004338</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>travco</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>28188</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>Quantum Home 2.0</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>Form</t>
+        </is>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>Closed - FILED</t>
+        </is>
+      </c>
+      <c r="P1034" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE1034" t="inlineStr">
+        <is>
+          <t>not_attempted</t>
+        </is>
+      </c>
+      <c r="AG1034" t="inlineStr">
+        <is>
+          <t>https://filingaccess.serff.com/sfa/filingSummary.xhtml?filingId=135004338</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
